--- a/sen_Vmax/IGD_Vmax_rank_result.xlsx
+++ b/sen_Vmax/IGD_Vmax_rank_result.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="78" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="75" uniqueCount="42">
   <si>
     <t>Problem</t>
   </si>
@@ -96,9 +96,6 @@
     <t>Vmax04</t>
   </si>
   <si>
-    <t>Vmax06</t>
-  </si>
-  <si>
     <t>Vmax08</t>
   </si>
   <si>
@@ -138,13 +135,13 @@
     <t>smaller value is better; rank 1 is the smallest mean value in each dataset row</t>
   </si>
   <si>
-    <t>F:\论文\MOPSO_PPHS\1.实验\sen_Vmax\IGD_Vmax.xlsx</t>
-  </si>
-  <si>
-    <t>F:\论文\MOPSO_PPHS\1.实验\sen_Vmax\IGD_Vmax_rank_result.xlsx</t>
-  </si>
-  <si>
-    <t>2026-06-10 16:46:22</t>
+    <t>F:\论文\MOPSO_PPHS\1.experiments\sen_Vmax\IGD_Vmax.xlsx</t>
+  </si>
+  <si>
+    <t>F:\论文\MOPSO_PPHS\1.experiments\sen_Vmax\IGD_Vmax_rank_result.xlsx</t>
+  </si>
+  <si>
+    <t>2026-06-11 14:03:41</t>
   </si>
 </sst>
 </file>
@@ -190,7 +187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="true"/>
@@ -200,8 +197,7 @@
     <col min="5" max="5" width="8.7109375" customWidth="true"/>
     <col min="6" max="6" width="8.7109375" customWidth="true"/>
     <col min="7" max="7" width="8.7109375" customWidth="true"/>
-    <col min="8" max="8" width="8.7109375" customWidth="true"/>
-    <col min="9" max="9" width="14.42578125" customWidth="true"/>
+    <col min="8" max="8" width="14.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -229,9 +225,6 @@
       <c r="H1" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="0" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -253,12 +246,9 @@
         <v>0.11441999999999999</v>
       </c>
       <c r="G2" s="0">
-        <v>0.11394</v>
+        <v>0.10771</v>
       </c>
       <c r="H2" s="0">
-        <v>0.10771</v>
-      </c>
-      <c r="I2" s="0">
         <v>0.10877000000000001</v>
       </c>
     </row>
@@ -282,12 +272,9 @@
         <v>0.19806000000000001</v>
       </c>
       <c r="G3" s="0">
-        <v>0.20588999999999999</v>
+        <v>0.20238</v>
       </c>
       <c r="H3" s="0">
-        <v>0.20238</v>
-      </c>
-      <c r="I3" s="0">
         <v>0.19450000000000001</v>
       </c>
     </row>
@@ -311,12 +298,9 @@
         <v>0.063436999999999993</v>
       </c>
       <c r="G4" s="0">
-        <v>0.06479</v>
+        <v>0.066919999999999993</v>
       </c>
       <c r="H4" s="0">
-        <v>0.066919999999999993</v>
-      </c>
-      <c r="I4" s="0">
         <v>0.065702999999999998</v>
       </c>
     </row>
@@ -340,12 +324,9 @@
         <v>0.041345</v>
       </c>
       <c r="G5" s="0">
-        <v>0.044395999999999998</v>
+        <v>0.045844999999999997</v>
       </c>
       <c r="H5" s="0">
-        <v>0.045844999999999997</v>
-      </c>
-      <c r="I5" s="0">
         <v>0.047251000000000001</v>
       </c>
     </row>
@@ -369,12 +350,9 @@
         <v>0.036348999999999999</v>
       </c>
       <c r="G6" s="0">
-        <v>0.039010999999999997</v>
+        <v>0.035770999999999997</v>
       </c>
       <c r="H6" s="0">
-        <v>0.035770999999999997</v>
-      </c>
-      <c r="I6" s="0">
         <v>0.036015999999999999</v>
       </c>
     </row>
@@ -398,12 +376,9 @@
         <v>0.043264999999999998</v>
       </c>
       <c r="G7" s="0">
-        <v>0.045235999999999998</v>
+        <v>0.043317000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>0.043317000000000001</v>
-      </c>
-      <c r="I7" s="0">
         <v>0.051669</v>
       </c>
     </row>
@@ -427,12 +402,9 @@
         <v>0.052242999999999998</v>
       </c>
       <c r="G8" s="0">
-        <v>0.049440999999999999</v>
+        <v>0.049036000000000003</v>
       </c>
       <c r="H8" s="0">
-        <v>0.049036000000000003</v>
-      </c>
-      <c r="I8" s="0">
         <v>0.048597000000000001</v>
       </c>
     </row>
@@ -456,12 +428,9 @@
         <v>0.029956</v>
       </c>
       <c r="G9" s="0">
-        <v>0.032601999999999999</v>
+        <v>0.032302999999999998</v>
       </c>
       <c r="H9" s="0">
-        <v>0.032302999999999998</v>
-      </c>
-      <c r="I9" s="0">
         <v>0.032883999999999997</v>
       </c>
     </row>
@@ -485,12 +454,9 @@
         <v>0.046165999999999999</v>
       </c>
       <c r="G10" s="0">
-        <v>0.040703000000000003</v>
+        <v>0.042852000000000001</v>
       </c>
       <c r="H10" s="0">
-        <v>0.042852000000000001</v>
-      </c>
-      <c r="I10" s="0">
         <v>0.044556999999999999</v>
       </c>
     </row>
@@ -514,12 +480,9 @@
         <v>0.090375999999999998</v>
       </c>
       <c r="G11" s="0">
-        <v>0.090448000000000001</v>
+        <v>0.090426000000000006</v>
       </c>
       <c r="H11" s="0">
-        <v>0.090426000000000006</v>
-      </c>
-      <c r="I11" s="0">
         <v>0.090137999999999996</v>
       </c>
     </row>
@@ -543,12 +506,9 @@
         <v>0.10405</v>
       </c>
       <c r="G12" s="0">
-        <v>0.095358999999999999</v>
+        <v>0.10020999999999999</v>
       </c>
       <c r="H12" s="0">
-        <v>0.10020999999999999</v>
-      </c>
-      <c r="I12" s="0">
         <v>0.091336000000000001</v>
       </c>
     </row>
@@ -572,12 +532,9 @@
         <v>0.080579999999999999</v>
       </c>
       <c r="G13" s="0">
-        <v>0.080574999999999994</v>
+        <v>0.08097</v>
       </c>
       <c r="H13" s="0">
-        <v>0.08097</v>
-      </c>
-      <c r="I13" s="0">
         <v>0.080633999999999997</v>
       </c>
     </row>
@@ -601,12 +558,9 @@
         <v>0.39032</v>
       </c>
       <c r="G14" s="0">
-        <v>0.37552000000000002</v>
+        <v>0.38290000000000002</v>
       </c>
       <c r="H14" s="0">
-        <v>0.38290000000000002</v>
-      </c>
-      <c r="I14" s="0">
         <v>0.36066999999999999</v>
       </c>
     </row>
@@ -630,12 +584,9 @@
         <v>0.082688999999999999</v>
       </c>
       <c r="G15" s="0">
-        <v>0.082700999999999997</v>
+        <v>0.082701999999999998</v>
       </c>
       <c r="H15" s="0">
-        <v>0.082701999999999998</v>
-      </c>
-      <c r="I15" s="0">
         <v>0.082167000000000004</v>
       </c>
     </row>
@@ -659,12 +610,9 @@
         <v>0.090513999999999997</v>
       </c>
       <c r="G16" s="0">
-        <v>0.090483999999999995</v>
+        <v>0.090515999999999999</v>
       </c>
       <c r="H16" s="0">
-        <v>0.090515999999999999</v>
-      </c>
-      <c r="I16" s="0">
         <v>0.089684</v>
       </c>
     </row>
@@ -688,12 +636,9 @@
         <v>0.065248</v>
       </c>
       <c r="G17" s="0">
-        <v>0.065239000000000005</v>
+        <v>0.065281000000000006</v>
       </c>
       <c r="H17" s="0">
-        <v>0.065281000000000006</v>
-      </c>
-      <c r="I17" s="0">
         <v>0.063958000000000001</v>
       </c>
     </row>
@@ -717,12 +662,9 @@
         <v>0.29791000000000001</v>
       </c>
       <c r="G18" s="0">
-        <v>0.29588999999999999</v>
+        <v>0.28711999999999999</v>
       </c>
       <c r="H18" s="0">
-        <v>0.28711999999999999</v>
-      </c>
-      <c r="I18" s="0">
         <v>0.28045999999999999</v>
       </c>
     </row>
@@ -746,12 +688,9 @@
         <v>0.17813000000000001</v>
       </c>
       <c r="G19" s="0">
-        <v>0.16772999999999999</v>
+        <v>0.16753999999999999</v>
       </c>
       <c r="H19" s="0">
-        <v>0.16753999999999999</v>
-      </c>
-      <c r="I19" s="0">
         <v>0.14945</v>
       </c>
     </row>
@@ -775,12 +714,9 @@
         <v>0.17831</v>
       </c>
       <c r="G20" s="0">
-        <v>0.15404000000000001</v>
+        <v>0.16313</v>
       </c>
       <c r="H20" s="0">
-        <v>0.16313</v>
-      </c>
-      <c r="I20" s="0">
         <v>0.13944999999999999</v>
       </c>
     </row>
@@ -804,12 +740,9 @@
         <v>0.32412000000000002</v>
       </c>
       <c r="G21" s="0">
-        <v>0.32217000000000001</v>
+        <v>0.33378999999999998</v>
       </c>
       <c r="H21" s="0">
-        <v>0.33378999999999998</v>
-      </c>
-      <c r="I21" s="0">
         <v>0.30726999999999999</v>
       </c>
     </row>
@@ -819,7 +752,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="true"/>
@@ -829,8 +762,7 @@
     <col min="5" max="5" width="8.140625" customWidth="true"/>
     <col min="6" max="6" width="8.140625" customWidth="true"/>
     <col min="7" max="7" width="8.140625" customWidth="true"/>
-    <col min="8" max="8" width="8.140625" customWidth="true"/>
-    <col min="9" max="9" width="14.42578125" customWidth="true"/>
+    <col min="8" max="8" width="14.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -858,9 +790,6 @@
       <c r="H1" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="0" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -876,18 +805,15 @@
         <v>3</v>
       </c>
       <c r="E2" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2" s="0">
-        <v>1</v>
-      </c>
-      <c r="I2" s="0">
         <v>2</v>
       </c>
     </row>
@@ -905,18 +831,15 @@
         <v>1</v>
       </c>
       <c r="E3" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="0">
         <v>3</v>
       </c>
       <c r="G3" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3" s="0">
-        <v>4</v>
-      </c>
-      <c r="I3" s="0">
         <v>2</v>
       </c>
     </row>
@@ -931,22 +854,19 @@
         <v>2000</v>
       </c>
       <c r="D4" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" s="0">
         <v>1</v>
       </c>
       <c r="G4" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" s="0">
-        <v>4</v>
-      </c>
-      <c r="I4" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -974,9 +894,6 @@
       <c r="H5" s="0">
         <v>5</v>
       </c>
-      <c r="I5" s="0">
-        <v>6</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
@@ -992,18 +909,15 @@
         <v>4</v>
       </c>
       <c r="E6" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" s="0">
         <v>3</v>
       </c>
       <c r="G6" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H6" s="0">
-        <v>1</v>
-      </c>
-      <c r="I6" s="0">
         <v>2</v>
       </c>
     </row>
@@ -1021,19 +935,16 @@
         <v>3</v>
       </c>
       <c r="E7" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" s="0">
         <v>1</v>
       </c>
       <c r="G7" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H7" s="0">
-        <v>2</v>
-      </c>
-      <c r="I7" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1047,21 +958,18 @@
         <v>10509</v>
       </c>
       <c r="D8" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="0">
-        <v>2</v>
-      </c>
-      <c r="I8" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1085,13 +993,10 @@
         <v>2</v>
       </c>
       <c r="G9" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H9" s="0">
-        <v>4</v>
-      </c>
-      <c r="I9" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1108,19 +1013,16 @@
         <v>1</v>
       </c>
       <c r="E10" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="0">
         <v>4</v>
-      </c>
-      <c r="I10" s="0">
-        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1134,21 +1036,18 @@
         <v>24526</v>
       </c>
       <c r="D11" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="0">
         <v>2</v>
       </c>
       <c r="G11" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H11" s="0">
-        <v>3</v>
-      </c>
-      <c r="I11" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1163,21 +1062,18 @@
         <v>22277</v>
       </c>
       <c r="D12" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="0">
-        <v>4</v>
-      </c>
-      <c r="I12" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1192,22 +1088,19 @@
         <v>22277</v>
       </c>
       <c r="D13" s="0">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E13" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" s="0">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="H13" s="0">
-        <v>6</v>
-      </c>
-      <c r="I13" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1227,15 +1120,12 @@
         <v>3</v>
       </c>
       <c r="F14" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" s="0">
         <v>4</v>
       </c>
       <c r="H14" s="0">
-        <v>5</v>
-      </c>
-      <c r="I14" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1262,9 +1152,6 @@
         <v>5</v>
       </c>
       <c r="H15" s="0">
-        <v>6</v>
-      </c>
-      <c r="I15" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1279,21 +1166,18 @@
         <v>29148</v>
       </c>
       <c r="D16" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H16" s="0">
-        <v>6</v>
-      </c>
-      <c r="I16" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1308,21 +1192,18 @@
         <v>22283</v>
       </c>
       <c r="D17" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" s="0">
-        <v>5</v>
-      </c>
-      <c r="I17" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1337,21 +1218,18 @@
         <v>22283</v>
       </c>
       <c r="D18" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="0">
-        <v>2</v>
-      </c>
-      <c r="I18" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1366,21 +1244,18 @@
         <v>12625</v>
       </c>
       <c r="D19" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" s="0">
-        <v>2</v>
-      </c>
-      <c r="I19" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1395,21 +1270,18 @@
         <v>12620</v>
       </c>
       <c r="D20" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F20" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="0">
-        <v>4</v>
-      </c>
-      <c r="I20" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1427,18 +1299,15 @@
         <v>2</v>
       </c>
       <c r="E21" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="0">
-        <v>5</v>
-      </c>
-      <c r="I21" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1448,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="true"/>
@@ -1457,18 +1326,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>29</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" s="0">
-        <v>2.2999999999999998</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1476,39 +1345,31 @@
         <v>23</v>
       </c>
       <c r="B3" s="0">
-        <v>2.9750000000000001</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" s="0">
-        <v>3.2749999999999999</v>
+        <v>3.2000000000000002</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="0">
-        <v>3.75</v>
+        <v>3.2000000000000002</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="0">
-        <v>3.7999999999999998</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="0">
-        <v>4.9000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -1521,44 +1382,44 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.140625" customWidth="true"/>
-    <col min="2" max="2" width="68.5703125" customWidth="true"/>
+    <col min="2" max="2" width="70" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="0">
         <v>20</v>
@@ -1566,18 +1427,18 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
